--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484322_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484322_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>17.5535</v>
+        <v>18.1292</v>
       </c>
       <c r="E2" t="n">
-        <v>15.5505</v>
+        <v>15.8539</v>
       </c>
       <c r="F2" t="n">
-        <v>2.003</v>
+        <v>2.2754</v>
       </c>
       <c r="G2" t="n">
         <v>14.1685</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0605</v>
+        <v>0.5152</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4704</v>
+        <v>-0.1671</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4099</v>
+        <v>0.6822</v>
       </c>
       <c r="V2" t="n">
         <v>1.8828</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1792</v>
+        <v>7.3196</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0008</v>
+        <v>4.4952</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1784</v>
+        <v>2.8244</v>
       </c>
       <c r="G3" t="n">
         <v>5.677</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2483</v>
+        <v>1.3887</v>
       </c>
       <c r="T3" t="n">
-        <v>0.743</v>
+        <v>0.2374</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5053</v>
+        <v>1.1513</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3321</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1483</v>
+        <v>6.5778</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7627</v>
+        <v>4.9479</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3856</v>
+        <v>1.6298</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0926</v>
+        <v>4.7965</v>
       </c>
       <c r="H4" t="n">
-        <v>0.295</v>
+        <v>-0.0061</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2023</v>
+        <v>4.8026</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1823</v>
+        <v>5.2163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9235</v>
+        <v>0.1433</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7412</v>
+        <v>5.073</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0897</v>
+        <v>-0.4198</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.1494</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5389</v>
+        <v>-0.2704</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8603</v>
+        <v>0.172</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1432</v>
+        <v>-0.5103</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7172</v>
+        <v>0.6822</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8853</v>
+        <v>5.6581</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7457</v>
+        <v>2.7627</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1396</v>
+        <v>2.8954</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7965</v>
+        <v>0.0926</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0061</v>
+        <v>0.295</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8026</v>
+        <v>-0.2023</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2163</v>
+        <v>0.1823</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1433</v>
+        <v>0.9235</v>
       </c>
       <c r="L5" t="n">
-        <v>5.073</v>
+        <v>-0.7412</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4198</v>
+        <v>-0.0897</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1494</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2704</v>
+        <v>0.5389</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5205</v>
+        <v>1.3701</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7125</v>
+        <v>0.1432</v>
       </c>
       <c r="U5" t="n">
-        <v>0.192</v>
+        <v>1.2269</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6212</v>
+        <v>3.2876</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0081</v>
+        <v>1.1162</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6131</v>
+        <v>2.1714</v>
       </c>
       <c r="G6" t="n">
-        <v>1.415</v>
+        <v>1.6747</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3728</v>
+        <v>2.4293</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9578</v>
+        <v>-0.7546</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0858</v>
+        <v>1.006</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6385</v>
+        <v>1.086</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5527</v>
+        <v>-0.0799</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3292</v>
+        <v>0.6687</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7342</v>
+        <v>1.3433</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>-0.6747</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9094</v>
+        <v>0.5228</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7705</v>
+        <v>0.1102</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1389</v>
+        <v>0.4126</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2735</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2018</v>
+        <v>2.6059</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5207</v>
+        <v>1.4014</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6812</v>
+        <v>1.2045</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6747</v>
+        <v>1.415</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4293</v>
+        <v>2.3728</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7546</v>
+        <v>-0.9578</v>
       </c>
       <c r="J7" t="n">
-        <v>1.006</v>
+        <v>1.0858</v>
       </c>
       <c r="K7" t="n">
-        <v>1.086</v>
+        <v>1.6385</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0799</v>
+        <v>-0.5527</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6687</v>
+        <v>0.3292</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3433</v>
+        <v>0.7342</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6747</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.437</v>
+        <v>0.8942</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5147</v>
+        <v>0.1638</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0776</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>1.2735</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4225</v>
+        <v>2.3058</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9052</v>
+        <v>1.0063</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5173</v>
+        <v>1.2994</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2275</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.892</v>
+        <v>0.7752</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0384</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9304</v>
+        <v>0.7125</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6216</v>
+        <v>1.8201</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5044</v>
+        <v>0.4033</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1172</v>
+        <v>1.4168</v>
       </c>
       <c r="G9" t="n">
         <v>1.7045</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.001</v>
+        <v>0.1974</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0989</v>
+        <v>-0.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0979</v>
+        <v>0.3975</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5904</v>
+        <v>1.3997</v>
       </c>
       <c r="E10" t="n">
         <v>1.4519</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1384</v>
+        <v>-0.0522</v>
       </c>
       <c r="G10" t="n">
         <v>0.8659</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5524</v>
+        <v>0.3618</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2283</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.5901</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9112</v>
+        <v>1.2029</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2217</v>
+        <v>0.3228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6894</v>
+        <v>0.8801</v>
       </c>
       <c r="G11" t="n">
         <v>1.96</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1893</v>
+        <v>0.1025</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0528</v>
+        <v>0.2434</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9232</v>
+        <v>-0.7638</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8132</v>
+        <v>-2.4088</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8901</v>
+        <v>1.6449</v>
       </c>
       <c r="G12" t="n">
         <v>0.2329</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4886</v>
+        <v>0.6479</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2888</v>
+        <v>0.1156</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7774</v>
+        <v>0.5323</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9442</v>
+        <v>-1.2752</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5133</v>
+        <v>-3.0077</v>
       </c>
       <c r="F13" t="n">
-        <v>1.569</v>
+        <v>1.7325</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6625</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4771</v>
+        <v>0.1919</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5447</v>
+        <v>-0.0391</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="V13" t="n">
         <v>1.2186</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>48.2676</v>
+        <v>48.2677</v>
       </c>
       <c r="E14" t="n">
-        <v>28.3452</v>
+        <v>28.3451</v>
       </c>
       <c r="F14" t="n">
-        <v>19.9223</v>
+        <v>19.9224</v>
       </c>
       <c r="G14" t="n">
         <v>28.6976</v>
@@ -1546,13 +1546,13 @@
         <v>14.6507</v>
       </c>
       <c r="S14" t="n">
-        <v>7.139600000000001</v>
+        <v>7.1397</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4526999999999997</v>
+        <v>-0.4529</v>
       </c>
       <c r="U14" t="n">
-        <v>7.592499999999999</v>
+        <v>7.5923</v>
       </c>
       <c r="V14" t="n">
         <v>5.5936</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2043</v>
+        <v>-3.2615</v>
       </c>
       <c r="E15" t="n">
         <v>-1.4839</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7204</v>
+        <v>-1.7776</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7866</v>
@@ -1624,13 +1624,13 @@
         <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3005</v>
+        <v>-0.3577</v>
       </c>
       <c r="T15" t="n">
         <v>-0.7868000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4863</v>
+        <v>0.4291</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5545</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.8487</v>
+        <v>-3.6308</v>
       </c>
       <c r="E16" t="n">
         <v>-0.533</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3157</v>
+        <v>-3.0978</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6541</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5777</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2262</v>
+        <v>-0.0083</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2186</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.8018</v>
+        <v>-4.2643</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7184</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0834</v>
+        <v>-3.6781</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2719</v>
+        <v>-3.9443</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1645</v>
+        <v>-2.2848</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1074</v>
+        <v>-1.6595</v>
       </c>
       <c r="J17" t="n">
-        <v>0.455</v>
+        <v>-0.0779</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6524</v>
+        <v>-1.3866</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1074</v>
+        <v>1.3087</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7269</v>
+        <v>-3.8664</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5121</v>
+        <v>-0.8982</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2148</v>
+        <v>-2.9682</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1159</v>
+        <v>-1.148</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1967</v>
+        <v>-1.1093</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0808</v>
+        <v>-0.0386</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.895</v>
+        <v>-4.3571</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2804</v>
+        <v>-1.5161</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6146</v>
+        <v>-2.841</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9113</v>
+        <v>-2.2719</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3888</v>
+        <v>-2.1645</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5225</v>
+        <v>-0.1074</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.878</v>
+        <v>0.455</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2443</v>
+        <v>-0.6524</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1074</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0334</v>
+        <v>-2.7269</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1445</v>
+        <v>-1.5121</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8889</v>
+        <v>-1.2148</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.007</v>
+        <v>-0.6713</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.9944</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2807</v>
+        <v>0.3232</v>
       </c>
       <c r="V18" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.0163</v>
+        <v>-4.624</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6873</v>
+        <v>-3.2804</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.329</v>
+        <v>-1.3436</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9443</v>
+        <v>-2.9113</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2848</v>
+        <v>-0.3888</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6595</v>
+        <v>-2.5225</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0779</v>
+        <v>-0.878</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3866</v>
+        <v>-0.2443</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3087</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8664</v>
+        <v>-2.0334</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8982</v>
+        <v>-0.1445</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.9682</v>
+        <v>-1.8889</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9</v>
+        <v>-0.736</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2105</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6895</v>
+        <v>-0.0097</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4209</v>
+        <v>-5.4287</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.046</v>
+        <v>-3.9449</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3749</v>
+        <v>-1.4839</v>
       </c>
       <c r="G20" t="n">
         <v>-5.26</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4028</v>
+        <v>-0.4106</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6987</v>
+        <v>-0.5976</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2959</v>
+        <v>0.187</v>
       </c>
       <c r="V20" t="n">
         <v>1.2186</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2313</v>
+        <v>-5.6232</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0983</v>
+        <v>-2.8961</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.133</v>
+        <v>-2.7271</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0112</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5792</v>
+        <v>-0.9712</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3645</v>
+        <v>-1.1622</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2148</v>
+        <v>0.1911</v>
       </c>
       <c r="V21" t="n">
         <v>-0.0549</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1294</v>
+        <v>-7.4055</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1939</v>
+        <v>-2.4972</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9356</v>
+        <v>-4.9083</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1575</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4798</v>
+        <v>-0.7559</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4621</v>
+        <v>-0.7654</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0177</v>
+        <v>0.0095</v>
       </c>
       <c r="V22" t="n">
         <v>-3.1014</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7199</v>
+        <v>-8.324199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8813</v>
+        <v>-3.1846</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.8386</v>
+        <v>-5.1396</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7006</v>
@@ -2248,13 +2248,13 @@
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4495</v>
+        <v>-0.1548</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5693</v>
+        <v>-0.8727</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0189</v>
+        <v>0.7179</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8828</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-48.26760000000001</v>
+        <v>-46.9193</v>
       </c>
       <c r="E24" t="n">
-        <v>-19.9225</v>
+        <v>-19.9224</v>
       </c>
       <c r="F24" t="n">
-        <v>-28.3452</v>
+        <v>-26.997</v>
       </c>
       <c r="G24" t="n">
         <v>-28.6975</v>
@@ -2299,19 +2299,19 @@
         <v>-20.9089</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1745000000000001</v>
+        <v>-0.1745000000000005</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1793</v>
+        <v>-0.1793000000000002</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004999999999999782</v>
+        <v>0.005000000000000226</v>
       </c>
       <c r="M24" t="n">
         <v>-28.5232</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.609300000000001</v>
+        <v>-7.609299999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-20.9139</v>
@@ -2323,16 +2323,16 @@
         <v>-14.6508</v>
       </c>
       <c r="R24" t="n">
-        <v>7.813700000000001</v>
+        <v>7.8137</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.1396</v>
+        <v>-5.7915</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.5926</v>
+        <v>-7.5924</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4529999999999998</v>
+        <v>1.8012</v>
       </c>
       <c r="V24" t="n">
         <v>-5.5936</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484322_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484322_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2876</v>
+        <v>2.6059</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1162</v>
+        <v>1.4014</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1714</v>
+        <v>1.2045</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6747</v>
+        <v>1.415</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4293</v>
+        <v>2.3728</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7546</v>
+        <v>-0.9578</v>
       </c>
       <c r="J6" t="n">
-        <v>1.006</v>
+        <v>1.0858</v>
       </c>
       <c r="K6" t="n">
-        <v>1.086</v>
+        <v>1.6385</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0799</v>
+        <v>-0.5527</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6687</v>
+        <v>0.3292</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3433</v>
+        <v>0.7342</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6747</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5228</v>
+        <v>0.8942</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1102</v>
+        <v>0.1638</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4126</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2772</v>
+        <v>1.2735</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2772</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6059</v>
+        <v>2.3058</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4014</v>
+        <v>1.0063</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2045</v>
+        <v>1.2994</v>
       </c>
       <c r="G7" t="n">
-        <v>1.415</v>
+        <v>-0.2275</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3728</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9578</v>
+        <v>-0.3237</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0858</v>
+        <v>0.6664</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6385</v>
+        <v>0.4502</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5527</v>
+        <v>0.2161</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3292</v>
+        <v>-0.8939</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7342</v>
+        <v>-0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4051</v>
+        <v>-0.5399</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8942</v>
+        <v>0.7752</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1638</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7125</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1052</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8317</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1068,72 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3058</v>
+        <v>2.1419</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0063</v>
+        <v>2.1419</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2994</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2275</v>
+        <v>2.1419</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09619999999999999</v>
+        <v>1.5349</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3237</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6664</v>
+        <v>2.1419</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4502</v>
+        <v>1.5349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2161</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8939</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7752</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7125</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7638</v>
+        <v>1.1457</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4088</v>
+        <v>-1.0257</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6449</v>
+        <v>2.1714</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2329</v>
+        <v>-0.4673</v>
       </c>
       <c r="H12" t="n">
-        <v>1.406</v>
+        <v>0.8944</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1731</v>
+        <v>-1.3616</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.571</v>
+        <v>-1.1359</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7368</v>
+        <v>-0.449</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3077</v>
+        <v>-0.6869</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6692</v>
+        <v>1.3433</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1346</v>
+        <v>-0.6747</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3674</v>
+        <v>1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6479</v>
+        <v>0.5228</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1156</v>
+        <v>0.1102</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5323</v>
+        <v>0.4126</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2772</v>
@@ -1406,12 +1461,17 @@
       </c>
       <c r="X12" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2752</v>
+        <v>-0.7638</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0077</v>
+        <v>-2.4088</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7325</v>
+        <v>1.6449</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6625</v>
+        <v>0.2329</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.802</v>
+        <v>1.406</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8604</v>
+        <v>-1.1731</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1872</v>
+        <v>-0.571</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6526</v>
+        <v>0.7368</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.5345</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1494</v>
+        <v>0.6692</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6741</v>
+        <v>0.1346</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1919</v>
+        <v>0.6479</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0391</v>
+        <v>0.1156</v>
       </c>
       <c r="U13" t="n">
-        <v>0.231</v>
+        <v>0.5323</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,151 +1566,157 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>48.2677</v>
+        <v>-1.2752</v>
       </c>
       <c r="E14" t="n">
-        <v>28.3451</v>
+        <v>-3.0077</v>
       </c>
       <c r="F14" t="n">
-        <v>19.9224</v>
+        <v>1.7325</v>
       </c>
       <c r="G14" t="n">
-        <v>28.6976</v>
+        <v>-3.6625</v>
       </c>
       <c r="H14" t="n">
-        <v>7.7887</v>
+        <v>-1.802</v>
       </c>
       <c r="I14" t="n">
-        <v>20.9091</v>
+        <v>-1.8604</v>
       </c>
       <c r="J14" t="n">
-        <v>28.5231</v>
+        <v>-4.1872</v>
       </c>
       <c r="K14" t="n">
-        <v>7.609300000000001</v>
+        <v>-1.6526</v>
       </c>
       <c r="L14" t="n">
-        <v>20.914</v>
+        <v>-2.5345</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1742999999999997</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1791999999999999</v>
+        <v>-0.1494</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.005099999999999993</v>
+        <v>0.6741</v>
       </c>
       <c r="P14" t="n">
-        <v>6.837</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.8136</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>14.6507</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>7.1397</v>
+        <v>0.1919</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4529</v>
+        <v>-0.0391</v>
       </c>
       <c r="U14" t="n">
-        <v>7.5923</v>
+        <v>0.231</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5936</v>
+        <v>1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>8.0885</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4949</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2615</v>
+        <v>48.2677</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4839</v>
+        <v>28.3451</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7776</v>
+        <v>19.9224</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7866</v>
+        <v>28.6975</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9811</v>
+        <v>7.7887</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7677</v>
+        <v>20.90910000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4517</v>
+        <v>28.5231</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3303</v>
+        <v>7.609200000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>20.914</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2382</v>
+        <v>0.1742999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3492</v>
+        <v>0.1792</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8891</v>
+        <v>-0.005099999999999993</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>6.837</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>-7.8136</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>14.6507</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3577</v>
+        <v>7.1397</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4529</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4291</v>
+        <v>7.592300000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5545</v>
+        <v>5.5936</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8.0885</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
-      </c>
+        <v>-2.4949</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.6308</v>
+        <v>-3.2615</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.533</v>
+        <v>-1.4839</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0978</v>
+        <v>-1.7776</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6541</v>
+        <v>-0.7866</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2208</v>
+        <v>0.9811</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8748</v>
+        <v>-1.7677</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1935</v>
+        <v>1.4517</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6398</v>
+        <v>1.3303</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5537</v>
+        <v>0.1214</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8476</v>
+        <v>-2.2382</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.419</v>
+        <v>-0.3492</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4285</v>
+        <v>-1.8891</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.586</v>
+        <v>-0.3577</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5777</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0083</v>
+        <v>0.4291</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.2643</v>
+        <v>-3.6308</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.533</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6781</v>
+        <v>-3.0978</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.9443</v>
+        <v>-0.6541</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2848</v>
+        <v>1.2208</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6595</v>
+        <v>-1.8748</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0779</v>
+        <v>2.1935</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3866</v>
+        <v>1.6398</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3087</v>
+        <v>0.5537</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8664</v>
+        <v>-2.8476</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8982</v>
+        <v>-0.419</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.9682</v>
+        <v>-2.4285</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.148</v>
+        <v>-0.586</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1093</v>
+        <v>-0.5777</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0386</v>
+        <v>-0.0083</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.3571</v>
+        <v>-4.2643</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5161</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.841</v>
+        <v>-3.6781</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2719</v>
+        <v>-3.9443</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1645</v>
+        <v>-2.2848</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1074</v>
+        <v>-1.6595</v>
       </c>
       <c r="J18" t="n">
-        <v>0.455</v>
+        <v>-0.0779</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6524</v>
+        <v>-1.3866</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1074</v>
+        <v>1.3087</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7269</v>
+        <v>-3.8664</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5121</v>
+        <v>-0.8982</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2148</v>
+        <v>-2.9682</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6713</v>
+        <v>-1.148</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9944</v>
+        <v>-1.1093</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3232</v>
+        <v>-0.0386</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.624</v>
+        <v>-4.3571</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2804</v>
+        <v>-1.5161</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3436</v>
+        <v>-2.841</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9113</v>
+        <v>-2.2719</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3888</v>
+        <v>-2.1645</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5225</v>
+        <v>-0.1074</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.878</v>
+        <v>0.455</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2443</v>
+        <v>-0.6524</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1074</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0334</v>
+        <v>-2.7269</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1445</v>
+        <v>-1.5121</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8889</v>
+        <v>-1.2148</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.736</v>
+        <v>-0.6713</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.9944</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0097</v>
+        <v>0.3232</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +2060,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4287</v>
+        <v>-4.624</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9449</v>
+        <v>-3.2804</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4839</v>
+        <v>-1.3436</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.26</v>
+        <v>-2.9113</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4454</v>
+        <v>-0.3888</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.8146</v>
+        <v>-2.5225</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6125</v>
+        <v>-0.878</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0435</v>
+        <v>-0.2443</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6559</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6476</v>
+        <v>-2.0334</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4889</v>
+        <v>-0.1445</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.1587</v>
+        <v>-1.8889</v>
       </c>
       <c r="P20" t="n">
         <v>-0.9767</v>
@@ -2014,28 +2105,33 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4106</v>
+        <v>-0.736</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5976</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.187</v>
+        <v>-0.0097</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6232</v>
+        <v>-5.4287</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8961</v>
+        <v>-3.9449</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7271</v>
+        <v>-1.4839</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0112</v>
+        <v>-5.26</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3244</v>
+        <v>-0.4454</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6867</v>
+        <v>-4.8146</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3349</v>
+        <v>-2.6125</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0771</v>
+        <v>0.0435</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7422</v>
+        <v>-2.6559</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6763</v>
+        <v>-2.6476</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2474</v>
+        <v>-0.4889</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.4289</v>
+        <v>-2.1587</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9712</v>
+        <v>-0.4106</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1622</v>
+        <v>-0.5976</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1911</v>
+        <v>0.187</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0549</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4055</v>
+        <v>-5.6232</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4972</v>
+        <v>-2.8961</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9083</v>
+        <v>-2.7271</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1575</v>
+        <v>-4.0112</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3093</v>
+        <v>-2.3244</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.4668</v>
+        <v>-1.6867</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1044</v>
+        <v>-0.3349</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4121</v>
+        <v>-1.0771</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3077</v>
+        <v>0.7422</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2619</v>
+        <v>-3.6763</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1028</v>
+        <v>-1.2474</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1591</v>
+        <v>-2.4289</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7559</v>
+        <v>-0.9712</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7654</v>
+        <v>-1.1622</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0095</v>
+        <v>0.1911</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.1014</v>
+        <v>-0.0549</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0.5545</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.324199999999999</v>
+        <v>-7.4055</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1846</v>
+        <v>-2.4972</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1396</v>
+        <v>-4.9083</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.7006</v>
+        <v>-3.1575</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6918</v>
+        <v>0.3093</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0089</v>
+        <v>-3.4668</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4758</v>
+        <v>0.1044</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2446</v>
+        <v>1.4121</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7688</v>
+        <v>-1.3077</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.2249</v>
+        <v>-3.2619</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4472</v>
+        <v>-1.1028</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.7777</v>
+        <v>-2.1591</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1548</v>
+        <v>-0.7559</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8727</v>
+        <v>-0.7654</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7179</v>
+        <v>0.0095</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8828</v>
+        <v>-3.1014</v>
       </c>
       <c r="W23" t="n">
         <v>-0.6642</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-8.324199999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.1846</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-5.1396</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-5.7006</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.6918</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.0089</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.4758</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.2446</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.7688</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-5.2249</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.4472</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-3.7777</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1548</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.8727</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484322_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-46.9193</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>-19.9224</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>-26.997</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>-28.6975</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>-7.788500000000001</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>-20.9089</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>-0.1745000000000005</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>-0.1793000000000002</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>0.005000000000000226</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>-28.5232</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-7.609299999999999</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>-20.9139</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>-6.8369</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-14.6508</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>7.8137</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>-5.7915</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>-7.5924</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>1.8012</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>-5.5936</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>2.495</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-8.0886</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
